--- a/BOM/KiCad.xlsx
+++ b/BOM/KiCad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\micro generator\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E126A2D-71FF-4A02-A66A-C39E9710AEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D7D8227-FFAA-471B-825C-6FDDE0FAD405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D53AA5D7-F6AB-49B9-8AA4-ABA019CF5B38}"/>
+    <workbookView xWindow="5205" yWindow="2805" windowWidth="21600" windowHeight="11835" xr2:uid="{AC382CA8-121A-4757-A1A1-BE9E5096CC43}"/>
   </bookViews>
   <sheets>
     <sheet name="KiCad" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Resistor_SMD:R_2512_6332Metric</t>
   </si>
   <si>
-    <t>R9,R10</t>
+    <t>R9,R10,R11</t>
   </si>
   <si>
     <t>10K</t>
@@ -1268,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC1A352-17B8-4FC9-93B0-A86A3359768B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C917745B-60DD-41A9-81A0-F7C3E9EE0FEB}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1583,7 +1583,7 @@
         <v>56</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>57</v>
